--- a/kahoot/orientation/finnish-history/main-periods-of-finnish-history-2-independent-finland__0005.xlsx
+++ b/kahoot/orientation/finnish-history/main-periods-of-finnish-history-2-independent-finland__0005.xlsx
@@ -1835,17 +1835,17 @@
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>Endast skolor</t>
+          <t>Bostadsbolag</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>Endast sjukhus</t>
+          <t>Hushåll</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>Endast kommuner</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="G9" s="14" t="n">
@@ -1892,17 +1892,17 @@
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>De ökade kraftigt</t>
+          <t>De hölls ungefär oförändrade</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>De blev gratis utan skatt</t>
+          <t>De privatiserades delvis</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>De avskaffades helt</t>
+          <t>De utökades genom nya reformer</t>
         </is>
       </c>
       <c r="G10" s="14" t="n">
@@ -1949,17 +1949,17 @@
       </c>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t>Den märktes inte</t>
+          <t>Den drabbade särskilt unga</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>Den gällde bara utlandet</t>
+          <t>Den drabbade främst företag och banker</t>
         </is>
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>Den var positiv för alla</t>
+          <t>Den märktes mest i vissa regioner</t>
         </is>
       </c>
       <c r="G11" s="14" t="n">
@@ -2006,17 +2006,17 @@
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>Sluta använda pengar</t>
+          <t>Höja skatter</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>Förbjuda handel</t>
+          <t>Minska offentliga utgifter</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>Stänga gränser</t>
+          <t>Skära ner investeringar</t>
         </is>
       </c>
       <c r="G12" s="14" t="n">
@@ -2063,17 +2063,17 @@
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>Återgång till stenåldern</t>
+          <t>Övergång till tjänstesamhälle</t>
         </is>
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>Avskaffande av internet</t>
+          <t>Övergång till industrisamhälle</t>
         </is>
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>Endast jordbruk igen</t>
+          <t>Övergång till kunskapssamhälle</t>
         </is>
       </c>
       <c r="G13" s="14" t="n">
@@ -2120,17 +2120,17 @@
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>Hästdragna vagnar</t>
+          <t>Telekom och elektronik</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>Ångmaskiner</t>
+          <t>Skogsindustrin</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>Båtar av trä</t>
+          <t>Byggsektorn</t>
         </is>
       </c>
       <c r="G14" s="14" t="n">
@@ -2177,17 +2177,17 @@
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>Förbud mot telefoner</t>
+          <t>Fax och personsökare</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>Inga datorer</t>
+          <t>Fasta telefoner</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>Mindre kommunikation</t>
+          <t>Postbrev och vykort</t>
         </is>
       </c>
       <c r="G15" s="14" t="n">
@@ -2234,17 +2234,17 @@
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>Kakao</t>
+          <t>Papper och kartong</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>Silke</t>
+          <t>Maskiner och utrustning</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>Bananer</t>
+          <t>Metallprodukter</t>
         </is>
       </c>
       <c r="G16" s="14" t="n">
@@ -2291,17 +2291,17 @@
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>De slutade exportera</t>
+          <t>De fokuserade mer på hemmamarknaden</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>De försvann</t>
+          <t>De minskade sin export</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>De blev bara lokala</t>
+          <t>De omstrukturerades och slogs ihop</t>
         </is>
       </c>
       <c r="G17" s="14" t="n">
@@ -2462,17 +2462,17 @@
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>Isolerade sig</t>
+          <t>Behöll en strikt neutral linje</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>Gick ur all handel</t>
+          <t>Fokuserade främst på Norden</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
         <is>
-          <t>Förbjöd resor</t>
+          <t>Prioriterade handeln med Ryssland</t>
         </is>
       </c>
       <c r="G20" s="14" t="n">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="F21" s="14" t="inlineStr">
         <is>
-          <t>EFTA bara</t>
+          <t>EFTA</t>
         </is>
       </c>
       <c r="G21" s="14" t="n">
@@ -2690,17 +2690,17 @@
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>Bara USA:s lagar</t>
+          <t>Europaparlamentets resolutioner</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>Endast kommunala regler</t>
+          <t>EU:s rekommendationer</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>Enbart NATO:s regler</t>
+          <t>Europarådets rekommendationer</t>
         </is>
       </c>
       <c r="G24" s="14" t="n">
@@ -2747,17 +2747,17 @@
       </c>
       <c r="D25" s="14" t="inlineStr">
         <is>
-          <t>Endast jordbrukspolitik</t>
+          <t>Jordbrukspolitik och regionalpolitik</t>
         </is>
       </c>
       <c r="E25" s="14" t="inlineStr">
         <is>
-          <t>Endast skolpolitik</t>
+          <t>Miljö- och energipolitik</t>
         </is>
       </c>
       <c r="F25" s="14" t="inlineStr">
         <is>
-          <t>Bara kulturpolitik</t>
+          <t>Utbildnings- och kulturpolitik</t>
         </is>
       </c>
       <c r="G25" s="14" t="n">
@@ -2804,17 +2804,17 @@
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>Genomförs utan samarbete</t>
+          <t>Sköts främst nationellt</t>
         </is>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>Styrs av ett annat land</t>
+          <t>Sköts främst inom NATO</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
         <is>
-          <t>Finns inte</t>
+          <t>Sköts främst genom FN</t>
         </is>
       </c>
       <c r="G26" s="14" t="n">
